--- a/data/trans_dic/P16A_n_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16A_n_R2-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas</t>
+          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,32; 19,85</t>
+          <t>14,5; 20,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,27; 31,38</t>
+          <t>24,28; 30,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,34; 25,49</t>
+          <t>19,43; 25,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28,84; 35,94</t>
+          <t>28,86; 36,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,0; 29,69</t>
+          <t>23,1; 30,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,87; 45,86</t>
+          <t>38,68; 45,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,96; 40,87</t>
+          <t>33,26; 40,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32,15; 44,45</t>
+          <t>31,35; 44,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,53; 23,9</t>
+          <t>19,6; 23,88</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32,26; 37,78</t>
+          <t>32,15; 37,47</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27,17; 32,06</t>
+          <t>27,36; 32,16</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>31,68; 39,12</t>
+          <t>32,83; 39,32</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,68; 20,8</t>
+          <t>15,77; 20,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,88; 27,87</t>
+          <t>21,83; 27,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20,68; 25,94</t>
+          <t>20,63; 25,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,52; 27,24</t>
+          <t>9,75; 26,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,06; 31,83</t>
+          <t>25,93; 32,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,62; 40,65</t>
+          <t>33,81; 40,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,93; 37,07</t>
+          <t>30,87; 37,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>37,79; 43,32</t>
+          <t>37,62; 42,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,5; 25,43</t>
+          <t>21,58; 25,56</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29,14; 33,29</t>
+          <t>29,07; 33,29</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26,45; 30,59</t>
+          <t>26,66; 30,73</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,93; 33,82</t>
+          <t>20,08; 33,68</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,74; 19,3</t>
+          <t>13,71; 19,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,92; 25,53</t>
+          <t>19,15; 25,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,14; 24,18</t>
+          <t>18,07; 24,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26,67; 34,24</t>
+          <t>26,48; 33,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,81; 34,71</t>
+          <t>27,78; 34,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,31; 42,73</t>
+          <t>35,54; 42,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,07; 34,28</t>
+          <t>27,0; 34,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35,43; 72,88</t>
+          <t>35,26; 75,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,42; 26,02</t>
+          <t>21,73; 26,23</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28,45; 33,3</t>
+          <t>28,57; 33,3</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23,67; 28,43</t>
+          <t>23,58; 28,15</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>32,7; 62,01</t>
+          <t>32,52; 60,37</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,45; 20,27</t>
+          <t>15,45; 20,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,65; 29,62</t>
+          <t>23,39; 29,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,88; 27,27</t>
+          <t>22,02; 27,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28,85; 35,22</t>
+          <t>28,92; 35,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,39; 35,06</t>
+          <t>28,79; 34,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,53; 44,82</t>
+          <t>38,67; 44,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,76; 40,83</t>
+          <t>34,61; 40,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>31,98; 43,51</t>
+          <t>32,49; 44,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,35; 27,41</t>
+          <t>23,46; 27,47</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32,32; 36,84</t>
+          <t>32,53; 37,13</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29,32; 33,8</t>
+          <t>29,37; 33,62</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>31,59; 38,74</t>
+          <t>32,25; 38,61</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,13; 18,69</t>
+          <t>16,14; 18,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23,8; 26,85</t>
+          <t>23,74; 26,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21,53; 24,43</t>
+          <t>21,45; 24,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22,24; 30,57</t>
+          <t>21,35; 30,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,15; 31,49</t>
+          <t>28,34; 31,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,38; 41,67</t>
+          <t>38,35; 41,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,07; 36,39</t>
+          <t>33,27; 36,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>38,68; 54,3</t>
+          <t>38,62; 53,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22,7; 24,77</t>
+          <t>22,67; 24,75</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31,64; 34,01</t>
+          <t>31,68; 33,94</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27,92; 30,15</t>
+          <t>27,81; 30,07</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>32,06; 41,87</t>
+          <t>32,31; 40,9</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas</t>
+          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>99360; 137739</t>
+          <t>100651; 139378</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>170744; 220734</t>
+          <t>170800; 216397</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>130477; 172032</t>
+          <t>131138; 173662</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>183236; 228353</t>
+          <t>183390; 229141</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>158317; 204352</t>
+          <t>158983; 207439</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>263997; 319647</t>
+          <t>269600; 319546</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>221785; 274957</t>
+          <t>223796; 275521</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>233178; 322430</t>
+          <t>227413; 319859</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>269920; 330373</t>
+          <t>270915; 330040</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>451868; 529112</t>
+          <t>450220; 524764</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>366157; 432061</t>
+          <t>368677; 433465</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>431118; 532311</t>
+          <t>446763; 534998</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>150857; 200015</t>
+          <t>151664; 200614</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>222744; 283703</t>
+          <t>222222; 278234</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>211440; 265178</t>
+          <t>210945; 263504</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>137471; 324948</t>
+          <t>116265; 320883</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>252325; 308244</t>
+          <t>251073; 311497</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>357388; 419581</t>
+          <t>348975; 416794</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>322572; 386639</t>
+          <t>321962; 386653</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>362320; 415260</t>
+          <t>360619; 412054</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>414917; 490756</t>
+          <t>416549; 493325</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>597362; 682436</t>
+          <t>595873; 682564</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>546383; 631692</t>
+          <t>550708; 634597</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>428793; 727598</t>
+          <t>432068; 724598</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>93243; 130959</t>
+          <t>92997; 131665</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>143306; 193395</t>
+          <t>145063; 193875</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>137805; 183666</t>
+          <t>137249; 185301</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>187919; 241275</t>
+          <t>186567; 236654</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>190180; 237346</t>
+          <t>189994; 238489</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>274419; 332069</t>
+          <t>276183; 333517</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>212497; 269063</t>
+          <t>211915; 267347</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>330669; 680252</t>
+          <t>329112; 705811</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>291802; 354440</t>
+          <t>296029; 357405</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>436636; 511089</t>
+          <t>438451; 511146</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>365545; 439158</t>
+          <t>364258; 434856</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>535607; 1015749</t>
+          <t>532692; 988850</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>145591; 190982</t>
+          <t>145594; 190829</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>224157; 280676</t>
+          <t>221700; 280517</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>205142; 255703</t>
+          <t>206428; 257473</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>267430; 326391</t>
+          <t>268077; 325198</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>305294; 364164</t>
+          <t>298968; 360596</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>405249; 471501</t>
+          <t>406729; 471945</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>362791; 426227</t>
+          <t>361216; 425669</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>350198; 476431</t>
+          <t>355721; 482392</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>462434; 542940</t>
+          <t>464669; 544111</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>646286; 736653</t>
+          <t>650557; 742505</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>580989; 669621</t>
+          <t>581851; 666082</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>638683; 783227</t>
+          <t>651981; 780673</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>528509; 612482</t>
+          <t>528764; 612259</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>815615; 920105</t>
+          <t>813379; 919139</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>730904; 829383</t>
+          <t>728195; 826325</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>769346; 1057510</t>
+          <t>738827; 1054383</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>951145; 1064005</t>
+          <t>957519; 1062880</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1365655; 1482575</t>
+          <t>1364502; 1482274</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1172285; 1289757</t>
+          <t>1179342; 1295341</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1435776; 2015906</t>
+          <t>1433857; 1977414</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1510894; 1648760</t>
+          <t>1508901; 1646994</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2210371; 2375709</t>
+          <t>2212676; 2370765</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1937437; 2091778</t>
+          <t>1929719; 2086393</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2299674; 3002654</t>
+          <t>2316995; 2933743</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A_n_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16A_n_R2-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>37,36%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,5; 20,08</t>
+          <t>14,46; 19,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,28; 30,76</t>
+          <t>24,03; 31,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,43; 25,74</t>
+          <t>19,25; 25,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28,86; 36,06</t>
+          <t>28,37; 36,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,1; 30,14</t>
+          <t>23,18; 29,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,68; 45,84</t>
+          <t>38,14; 45,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,26; 40,95</t>
+          <t>33,02; 40,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31,35; 44,1</t>
+          <t>39,34; 45,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,6; 23,88</t>
+          <t>19,58; 23,86</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32,15; 37,47</t>
+          <t>32,01; 37,3</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27,36; 32,16</t>
+          <t>27,15; 32,23</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32,83; 39,32</t>
+          <t>35,12; 39,73</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>32,96%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,77; 20,86</t>
+          <t>15,79; 20,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,83; 27,33</t>
+          <t>22,0; 27,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20,63; 25,77</t>
+          <t>20,67; 26,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,75; 26,9</t>
+          <t>23,04; 29,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,93; 32,17</t>
+          <t>25,79; 31,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,81; 40,38</t>
+          <t>34,42; 40,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,87; 37,07</t>
+          <t>31,09; 37,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>37,62; 42,98</t>
+          <t>37,21; 42,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,58; 25,56</t>
+          <t>21,57; 25,44</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29,07; 33,29</t>
+          <t>28,98; 33,19</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26,66; 30,73</t>
+          <t>26,57; 30,63</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,08; 33,68</t>
+          <t>31,08; 34,93</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>34,01%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,71; 19,41</t>
+          <t>13,59; 19,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,15; 25,59</t>
+          <t>19,45; 25,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,07; 24,4</t>
+          <t>18,21; 24,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26,48; 33,58</t>
+          <t>27,17; 34,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,78; 34,87</t>
+          <t>27,47; 34,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,54; 42,91</t>
+          <t>35,35; 42,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,0; 34,06</t>
+          <t>27,2; 34,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35,26; 75,62</t>
+          <t>34,75; 40,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,73; 26,23</t>
+          <t>21,6; 26,0</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28,57; 33,3</t>
+          <t>28,24; 33,35</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23,58; 28,15</t>
+          <t>23,41; 28,05</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>32,52; 60,37</t>
+          <t>31,74; 36,56</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,86%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,45; 20,25</t>
+          <t>15,58; 20,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,39; 29,6</t>
+          <t>23,91; 30,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,02; 27,46</t>
+          <t>21,83; 27,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28,92; 35,09</t>
+          <t>28,35; 34,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,79; 34,72</t>
+          <t>29,27; 34,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,67; 44,87</t>
+          <t>38,81; 44,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,61; 40,78</t>
+          <t>34,75; 41,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>32,49; 44,06</t>
+          <t>39,29; 44,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,46; 27,47</t>
+          <t>23,36; 27,25</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32,53; 37,13</t>
+          <t>32,5; 36,87</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29,37; 33,62</t>
+          <t>29,41; 33,78</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32,25; 38,61</t>
+          <t>34,95; 38,86</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,19%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,14; 18,69</t>
+          <t>16,23; 18,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23,74; 26,82</t>
+          <t>23,61; 26,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21,45; 24,34</t>
+          <t>21,54; 24,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21,35; 30,48</t>
+          <t>28,07; 31,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,34; 31,45</t>
+          <t>28,31; 31,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,35; 41,66</t>
+          <t>38,48; 41,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,27; 36,54</t>
+          <t>33,21; 36,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>38,62; 53,27</t>
+          <t>39,05; 41,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22,67; 24,75</t>
+          <t>22,64; 24,8</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31,68; 33,94</t>
+          <t>31,65; 33,87</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27,81; 30,07</t>
+          <t>27,94; 30,08</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>32,31; 40,9</t>
+          <t>34,06; 36,27</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>204999</t>
+          <t>221870</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>290915</t>
+          <t>310487</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>495914</t>
+          <t>532357</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>100651; 139378</t>
+          <t>100357; 138016</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>170800; 216397</t>
+          <t>169057; 218399</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>131138; 173662</t>
+          <t>129873; 175323</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>183390; 229141</t>
+          <t>195936; 249126</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>158983; 207439</t>
+          <t>159539; 203540</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>269600; 319546</t>
+          <t>265878; 318118</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>223796; 275521</t>
+          <t>222175; 271002</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>227413; 319859</t>
+          <t>288827; 332757</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>270915; 330040</t>
+          <t>270610; 329805</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>450220; 524764</t>
+          <t>448264; 522324</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>368677; 433465</t>
+          <t>365869; 434323</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>446763; 534998</t>
+          <t>500357; 566159</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>247304</t>
+          <t>271903</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>386266</t>
+          <t>426984</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>633571</t>
+          <t>698887</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>151664; 200614</t>
+          <t>151853; 197686</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>222222; 278234</t>
+          <t>223909; 281816</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>210945; 263504</t>
+          <t>211385; 269342</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>116265; 320883</t>
+          <t>241699; 305411</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>251073; 311497</t>
+          <t>249776; 308232</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>348975; 416794</t>
+          <t>355286; 423060</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>321962; 386653</t>
+          <t>324222; 388758</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>360619; 412054</t>
+          <t>398674; 453628</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>416549; 493325</t>
+          <t>416369; 491080</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>595873; 682564</t>
+          <t>594117; 680341</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>550708; 634597</t>
+          <t>548848; 632683</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>432068; 724598</t>
+          <t>658918; 740691</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>213022</t>
+          <t>242894</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>472150</t>
+          <t>306405</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>685172</t>
+          <t>549298</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>92997; 131665</t>
+          <t>92195; 130551</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>145063; 193875</t>
+          <t>147378; 196529</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>137249; 185301</t>
+          <t>138312; 184272</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>186567; 236654</t>
+          <t>218222; 274696</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>189994; 238489</t>
+          <t>187881; 235115</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>276183; 333517</t>
+          <t>274712; 331364</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>211915; 267347</t>
+          <t>213540; 267564</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>329112; 705811</t>
+          <t>282238; 329853</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>296029; 357405</t>
+          <t>294222; 354243</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>438451; 511146</t>
+          <t>433405; 511804</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>364258; 434856</t>
+          <t>361629; 433237</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>532692; 988850</t>
+          <t>512626; 590554</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>296006</t>
+          <t>309898</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>437336</t>
+          <t>467450</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>733342</t>
+          <t>777348</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>145594; 190829</t>
+          <t>146758; 189371</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>221700; 280517</t>
+          <t>226647; 286030</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>206428; 257473</t>
+          <t>204668; 256646</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>268077; 325198</t>
+          <t>280639; 339944</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>298968; 360596</t>
+          <t>304002; 363341</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>406729; 471945</t>
+          <t>408262; 470545</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>361216; 425669</t>
+          <t>362670; 431438</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>355721; 482392</t>
+          <t>439670; 498310</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>464669; 544111</t>
+          <t>462790; 539811</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>650557; 742505</t>
+          <t>649932; 737233</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>581851; 666082</t>
+          <t>582784; 669317</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>651981; 780673</t>
+          <t>737152; 819626</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>961331</t>
+          <t>1046564</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1586668</t>
+          <t>1511326</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2547999</t>
+          <t>2557890</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>528764; 612259</t>
+          <t>531817; 613638</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>813379; 919139</t>
+          <t>809215; 914675</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>728195; 826325</t>
+          <t>731051; 828740</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>738827; 1054383</t>
+          <t>991785; 1110818</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>957519; 1062880</t>
+          <t>956577; 1067183</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1364502; 1482274</t>
+          <t>1369206; 1483275</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1179342; 1295341</t>
+          <t>1177292; 1295952</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1433857; 1977414</t>
+          <t>1459245; 1566536</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1508901; 1646994</t>
+          <t>1507175; 1650446</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2212676; 2370765</t>
+          <t>2210844; 2366137</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1929719; 2086393</t>
+          <t>1938917; 2087176</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2316995; 2933743</t>
+          <t>2475849; 2636790</t>
         </is>
       </c>
     </row>
